--- a/smart_pig_demo/行业新闻与咨询投稿登记表.xlsx
+++ b/smart_pig_demo/行业新闻与咨询投稿登记表.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -699,6 +699,76 @@
         </is>
       </c>
     </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-24 02:43:31</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>王工程师</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>现代农牧智能化研究院</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>13812345678</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>wx_wang_ai</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>wang@ai-livestock.com</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>💻 智慧畜牧工程与数字化档案</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>基于边缘计算与机器视觉的母猪发情智能巡检系统实操报告</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>通过安装于母猪限位栏上方的双目摄像头与边缘计算盒子，实现对母猪爬跨行为与外阴充血的24小时自动识别。</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>无附件</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>待初审对接</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>大屏在线投稿自动登记入库</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:N1"/>

--- a/smart_pig_demo/行业新闻与咨询投稿登记表.xlsx
+++ b/smart_pig_demo/行业新闻与咨询投稿登记表.xlsx
@@ -461,12 +461,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -476,8 +476,7 @@
     <col width="35" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
     <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -550,11 +549,6 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>处理状态</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
           <t>处理意见与对接记录</t>
         </is>
       </c>
@@ -565,17 +559,17 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-23 14:08:49</t>
+          <t>2026-10-23 12:00:00</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>李尧</t>
+          <t>李尧【示范样本】</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>西北农林科技大学动物科技学院</t>
+          <t>西北农林科技大学动物科技学院【示范】</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -600,178 +594,33 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>智慧牧业数字化生产档案与多畜种核心指标管理实践</t>
+          <t>【示范样本】智慧牧业数字化生产档案与多畜种核心指标管理实践</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>首套覆盖生猪、奶牛、肉牛、奶山羊、肉羊、皮用羊、蛋鸡、肉鸡八大核心畜禽法定养殖档案与指标计算引擎，实现行业新闻与生产台账双向闭环。</t>
+          <t>【系统预置示范样本，非正式用户投稿】首套覆盖生猪、奶牛、肉牛、奶山羊、肉羊、皮用羊、蛋鸡、肉鸡八大核心畜禽法定养殖档案与指标计算引擎，实现行业新闻与生产台账双向闭环。</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>无附件</t>
+          <t>示范附件_智慧畜牧数字化生产档案指南.pdf</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>投稿附件/示范附件_智慧畜牧数字化生产档案指南.pdf</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>待初审对接</t>
-        </is>
-      </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>大屏在线投稿自动登记入库</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-23 14:08:49</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>张专家</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>国家肉牛牦牛产业技术体系</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>13900112233</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>未填写</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>未填写</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>🐖 生猪产业与精细化管理</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>现代肉牛高效TMR精准饲喂与肉品质提升研究</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>无摘要</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>无附件</t>
-        </is>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>待初审对接</t>
-        </is>
-      </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>大屏在线投稿自动登记入库</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-24 02:43:31</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>王工程师</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>现代农牧智能化研究院</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>13812345678</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>wx_wang_ai</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>wang@ai-livestock.com</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>💻 智慧畜牧工程与数字化档案</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>基于边缘计算与机器视觉的母猪发情智能巡检系统实操报告</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>通过安装于母猪限位栏上方的双目摄像头与边缘计算盒子，实现对母猪爬跨行为与外阴充血的24小时自动识别。</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>无附件</t>
-        </is>
-      </c>
-      <c r="L5" s="4" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>待初审对接</t>
-        </is>
-      </c>
-      <c r="N5" s="4" t="inlineStr">
-        <is>
-          <t>大屏在线投稿自动登记入库</t>
+          <t>【系统预置示范样本 · 请勿删除】用于展示台账录入格式与规范示例。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
